--- a/output/yearly_total_coral_cover_iteration_83_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_83_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.257762571576882</v>
+        <v>1.274550457319503</v>
       </c>
       <c r="C3" t="n">
-        <v>4.579889256036589</v>
+        <v>4.646775727126924</v>
       </c>
       <c r="D3" t="n">
-        <v>6.035181204805919</v>
+        <v>6.161875746038969</v>
       </c>
       <c r="E3" t="n">
-        <v>11.87283303241939</v>
+        <v>12.0832019304854</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.388524963591072</v>
+        <v>1.427061714068808</v>
       </c>
       <c r="C4" t="n">
-        <v>4.977769957774009</v>
+        <v>5.155807353816577</v>
       </c>
       <c r="D4" t="n">
-        <v>6.209905338606669</v>
+        <v>6.41780580089712</v>
       </c>
       <c r="E4" t="n">
-        <v>12.57620025997175</v>
+        <v>13.00067486878251</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.571432725785955</v>
+        <v>1.629341403385777</v>
       </c>
       <c r="C5" t="n">
-        <v>5.451923118047918</v>
+        <v>5.836841137791787</v>
       </c>
       <c r="D5" t="n">
-        <v>6.453693332637491</v>
+        <v>6.822814512343292</v>
       </c>
       <c r="E5" t="n">
-        <v>13.47704917647136</v>
+        <v>14.28899705352086</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.778862342369888</v>
+        <v>1.866760156598662</v>
       </c>
       <c r="C6" t="n">
-        <v>6.016238533622711</v>
+        <v>6.681580800622873</v>
       </c>
       <c r="D6" t="n">
-        <v>6.693981229947177</v>
+        <v>7.234436560714351</v>
       </c>
       <c r="E6" t="n">
-        <v>14.48908210593978</v>
+        <v>15.78277751793589</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.022081408179219</v>
+        <v>2.141453851671201</v>
       </c>
       <c r="C7" t="n">
-        <v>6.739008600236234</v>
+        <v>7.694438118346668</v>
       </c>
       <c r="D7" t="n">
-        <v>7.040046948068847</v>
+        <v>7.668027813589347</v>
       </c>
       <c r="E7" t="n">
-        <v>15.8011369564843</v>
+        <v>17.50391978360722</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.262659703376618</v>
+        <v>1.349161813396984</v>
       </c>
       <c r="C8" t="n">
-        <v>4.493600437987917</v>
+        <v>5.38182928798128</v>
       </c>
       <c r="D8" t="n">
-        <v>5.326799542518721</v>
+        <v>5.862686160692123</v>
       </c>
       <c r="E8" t="n">
-        <v>11.08305968388326</v>
+        <v>12.59367726207039</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.603391461601597</v>
+        <v>1.697933893125254</v>
       </c>
       <c r="C9" t="n">
-        <v>5.587746673093364</v>
+        <v>6.635281109959346</v>
       </c>
       <c r="D9" t="n">
-        <v>5.796062703433897</v>
+        <v>6.345082974535884</v>
       </c>
       <c r="E9" t="n">
-        <v>12.98720083812886</v>
+        <v>14.67829797762048</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.964940413623729</v>
+        <v>2.050469575364525</v>
       </c>
       <c r="C10" t="n">
-        <v>6.87022673709033</v>
+        <v>8.087120243531317</v>
       </c>
       <c r="D10" t="n">
-        <v>6.265545136939136</v>
+        <v>6.783764730892189</v>
       </c>
       <c r="E10" t="n">
-        <v>15.1007122876532</v>
+        <v>16.92135454978803</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.326112651183726</v>
+        <v>2.412932102787575</v>
       </c>
       <c r="C11" t="n">
-        <v>8.260823900687239</v>
+        <v>9.633718218292115</v>
       </c>
       <c r="D11" t="n">
-        <v>6.815762576260087</v>
+        <v>7.304303507133501</v>
       </c>
       <c r="E11" t="n">
-        <v>17.40269912813105</v>
+        <v>19.35095382821319</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.706244294813679</v>
+        <v>2.775785595794333</v>
       </c>
       <c r="C12" t="n">
-        <v>9.733551717951402</v>
+        <v>11.26022463391126</v>
       </c>
       <c r="D12" t="n">
-        <v>7.286619576576333</v>
+        <v>7.819755198835354</v>
       </c>
       <c r="E12" t="n">
-        <v>19.72641558934141</v>
+        <v>21.85576542854095</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.083354272937956</v>
+        <v>3.111783157586688</v>
       </c>
       <c r="C13" t="n">
-        <v>11.25214087038112</v>
+        <v>12.94598300456618</v>
       </c>
       <c r="D13" t="n">
-        <v>7.733369952239117</v>
+        <v>8.272240881264079</v>
       </c>
       <c r="E13" t="n">
-        <v>22.06886509555819</v>
+        <v>24.33000704341694</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.791601202957047</v>
+        <v>1.793289809008351</v>
       </c>
       <c r="C14" t="n">
-        <v>7.794320825987404</v>
+        <v>9.065772460280405</v>
       </c>
       <c r="D14" t="n">
-        <v>5.934488157585204</v>
+        <v>6.244985504007343</v>
       </c>
       <c r="E14" t="n">
-        <v>15.52041018652965</v>
+        <v>17.1040477732961</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.851507447870187</v>
+        <v>1.82677722320021</v>
       </c>
       <c r="C15" t="n">
-        <v>8.460043944237167</v>
+        <v>9.854960169816247</v>
       </c>
       <c r="D15" t="n">
-        <v>5.955546645841298</v>
+        <v>6.246242141068779</v>
       </c>
       <c r="E15" t="n">
-        <v>16.26709803794865</v>
+        <v>17.92797953408524</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.164439528598858</v>
+        <v>2.112838869263646</v>
       </c>
       <c r="C16" t="n">
-        <v>9.999493066835463</v>
+        <v>11.65467060881037</v>
       </c>
       <c r="D16" t="n">
-        <v>6.402163311457257</v>
+        <v>6.656691221260285</v>
       </c>
       <c r="E16" t="n">
-        <v>18.56609590689158</v>
+        <v>20.4242006993343</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.744251511181223</v>
+        <v>1.687840288095202</v>
       </c>
       <c r="C17" t="n">
-        <v>9.273863703672561</v>
+        <v>10.74072240101885</v>
       </c>
       <c r="D17" t="n">
-        <v>5.941105137111828</v>
+        <v>6.156166789204134</v>
       </c>
       <c r="E17" t="n">
-        <v>16.95922035196561</v>
+        <v>18.58472947831818</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.010560393435213</v>
+        <v>1.921358797027348</v>
       </c>
       <c r="C18" t="n">
-        <v>10.82389606652264</v>
+        <v>12.5142005413555</v>
       </c>
       <c r="D18" t="n">
-        <v>6.34099061200564</v>
+        <v>6.541316231057201</v>
       </c>
       <c r="E18" t="n">
-        <v>19.17544707196349</v>
+        <v>20.97687556944005</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.03847148066695</v>
+        <v>1.919483658912236</v>
       </c>
       <c r="C19" t="n">
-        <v>11.58522177621195</v>
+        <v>13.38168263030502</v>
       </c>
       <c r="D19" t="n">
-        <v>6.419805317702572</v>
+        <v>6.601870429455144</v>
       </c>
       <c r="E19" t="n">
-        <v>20.04349857458148</v>
+        <v>21.9030367186724</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.304318941499944</v>
+        <v>2.127947966432004</v>
       </c>
       <c r="C20" t="n">
-        <v>13.30653966102197</v>
+        <v>15.31690370491633</v>
       </c>
       <c r="D20" t="n">
-        <v>6.850615845280158</v>
+        <v>6.971174463361666</v>
       </c>
       <c r="E20" t="n">
-        <v>22.46147444780207</v>
+        <v>24.41602613471</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.389683510315445</v>
+        <v>1.260672044500372</v>
       </c>
       <c r="C21" t="n">
-        <v>9.734175749762763</v>
+        <v>11.18612169948154</v>
       </c>
       <c r="D21" t="n">
-        <v>5.711444896657372</v>
+        <v>5.787392899057906</v>
       </c>
       <c r="E21" t="n">
-        <v>16.83530415673558</v>
+        <v>18.23418664303982</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_83_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_83_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.274550457319503</v>
+        <v>1.265920894999173</v>
       </c>
       <c r="C3" t="n">
-        <v>4.646775727126924</v>
+        <v>4.584464200338379</v>
       </c>
       <c r="D3" t="n">
-        <v>6.161875746038969</v>
+        <v>6.101517897181875</v>
       </c>
       <c r="E3" t="n">
-        <v>12.0832019304854</v>
+        <v>11.95190299251943</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.427061714068808</v>
+        <v>1.409059329770022</v>
       </c>
       <c r="C4" t="n">
-        <v>5.155807353816577</v>
+        <v>5.018735742334273</v>
       </c>
       <c r="D4" t="n">
-        <v>6.41780580089712</v>
+        <v>6.323865010554353</v>
       </c>
       <c r="E4" t="n">
-        <v>13.00067486878251</v>
+        <v>12.75166008265865</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.629341403385777</v>
+        <v>1.602583396453214</v>
       </c>
       <c r="C5" t="n">
-        <v>5.836841137791787</v>
+        <v>5.571794519692975</v>
       </c>
       <c r="D5" t="n">
-        <v>6.822814512343292</v>
+        <v>6.673849699871101</v>
       </c>
       <c r="E5" t="n">
-        <v>14.28899705352086</v>
+        <v>13.84822761601729</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.866760156598662</v>
+        <v>1.841969546528976</v>
       </c>
       <c r="C6" t="n">
-        <v>6.681580800622873</v>
+        <v>6.252525442391349</v>
       </c>
       <c r="D6" t="n">
-        <v>7.234436560714351</v>
+        <v>7.088242410762389</v>
       </c>
       <c r="E6" t="n">
-        <v>15.78277751793589</v>
+        <v>15.18273739968271</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.141453851671201</v>
+        <v>2.119162018300665</v>
       </c>
       <c r="C7" t="n">
-        <v>7.694438118346668</v>
+        <v>7.055066526056532</v>
       </c>
       <c r="D7" t="n">
-        <v>7.668027813589347</v>
+        <v>7.488569792779955</v>
       </c>
       <c r="E7" t="n">
-        <v>17.50391978360722</v>
+        <v>16.66279833713715</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.349161813396984</v>
+        <v>1.376681997498973</v>
       </c>
       <c r="C8" t="n">
-        <v>5.38182928798128</v>
+        <v>4.778304451998786</v>
       </c>
       <c r="D8" t="n">
-        <v>5.862686160692123</v>
+        <v>5.784526270221582</v>
       </c>
       <c r="E8" t="n">
-        <v>12.59367726207039</v>
+        <v>11.93951271971934</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.697933893125254</v>
+        <v>1.769970822636691</v>
       </c>
       <c r="C9" t="n">
-        <v>6.635281109959346</v>
+        <v>5.903422036189775</v>
       </c>
       <c r="D9" t="n">
-        <v>6.345082974535884</v>
+        <v>6.36654579052012</v>
       </c>
       <c r="E9" t="n">
-        <v>14.67829797762048</v>
+        <v>14.03993864934659</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.050469575364525</v>
+        <v>2.176287177182393</v>
       </c>
       <c r="C10" t="n">
-        <v>8.087120243531317</v>
+        <v>7.215529053485932</v>
       </c>
       <c r="D10" t="n">
-        <v>6.783764730892189</v>
+        <v>6.917480635209684</v>
       </c>
       <c r="E10" t="n">
-        <v>16.92135454978803</v>
+        <v>16.30929686587801</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.412932102787575</v>
+        <v>2.576405586999234</v>
       </c>
       <c r="C11" t="n">
-        <v>9.633718218292115</v>
+        <v>8.698533504308587</v>
       </c>
       <c r="D11" t="n">
-        <v>7.304303507133501</v>
+        <v>7.565952397612882</v>
       </c>
       <c r="E11" t="n">
-        <v>19.35095382821319</v>
+        <v>18.8408914889207</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.775785595794333</v>
+        <v>2.971112409465879</v>
       </c>
       <c r="C12" t="n">
-        <v>11.26022463391126</v>
+        <v>10.32418966640209</v>
       </c>
       <c r="D12" t="n">
-        <v>7.819755198835354</v>
+        <v>8.178216391046476</v>
       </c>
       <c r="E12" t="n">
-        <v>21.85576542854095</v>
+        <v>21.47351846691444</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.111783157586688</v>
+        <v>3.356878599672531</v>
       </c>
       <c r="C13" t="n">
-        <v>12.94598300456618</v>
+        <v>12.03192569932913</v>
       </c>
       <c r="D13" t="n">
-        <v>8.272240881264079</v>
+        <v>8.808454313522692</v>
       </c>
       <c r="E13" t="n">
-        <v>24.33000704341694</v>
+        <v>24.19725861252435</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.793289809008351</v>
+        <v>1.921280257211008</v>
       </c>
       <c r="C14" t="n">
-        <v>9.065772460280405</v>
+        <v>8.446515460872646</v>
       </c>
       <c r="D14" t="n">
-        <v>6.244985504007343</v>
+        <v>6.708419507797051</v>
       </c>
       <c r="E14" t="n">
-        <v>17.1040477732961</v>
+        <v>17.07621522588071</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.82677722320021</v>
+        <v>1.97598323929164</v>
       </c>
       <c r="C15" t="n">
-        <v>9.854960169816247</v>
+        <v>9.350518564420151</v>
       </c>
       <c r="D15" t="n">
-        <v>6.246242141068779</v>
+        <v>6.802510207772063</v>
       </c>
       <c r="E15" t="n">
-        <v>17.92797953408524</v>
+        <v>18.12901201148386</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.112838869263646</v>
+        <v>2.297093278396687</v>
       </c>
       <c r="C16" t="n">
-        <v>11.65467060881037</v>
+        <v>11.17666746908964</v>
       </c>
       <c r="D16" t="n">
-        <v>6.656691221260285</v>
+        <v>7.357158390763344</v>
       </c>
       <c r="E16" t="n">
-        <v>20.4242006993343</v>
+        <v>20.83091913824967</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.687840288095202</v>
+        <v>1.84682451132093</v>
       </c>
       <c r="C17" t="n">
-        <v>10.74072240101885</v>
+        <v>10.46604902832468</v>
       </c>
       <c r="D17" t="n">
-        <v>6.156166789204134</v>
+        <v>6.892644464498965</v>
       </c>
       <c r="E17" t="n">
-        <v>18.58472947831818</v>
+        <v>19.20551800414457</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.921358797027348</v>
+        <v>2.113555545087746</v>
       </c>
       <c r="C18" t="n">
-        <v>12.5142005413555</v>
+        <v>12.27864981467556</v>
       </c>
       <c r="D18" t="n">
-        <v>6.541316231057201</v>
+        <v>7.392756562519331</v>
       </c>
       <c r="E18" t="n">
-        <v>20.97687556944005</v>
+        <v>21.78496192228264</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.919483658912236</v>
+        <v>2.122577806489774</v>
       </c>
       <c r="C19" t="n">
-        <v>13.38168263030502</v>
+        <v>13.17492656379064</v>
       </c>
       <c r="D19" t="n">
-        <v>6.601870429455144</v>
+        <v>7.528502817585538</v>
       </c>
       <c r="E19" t="n">
-        <v>21.9030367186724</v>
+        <v>22.82600718786595</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.127947966432004</v>
+        <v>2.359493162478615</v>
       </c>
       <c r="C20" t="n">
-        <v>15.31690370491633</v>
+        <v>15.13132393638256</v>
       </c>
       <c r="D20" t="n">
-        <v>6.971174463361666</v>
+        <v>8.026101641483034</v>
       </c>
       <c r="E20" t="n">
-        <v>24.41602613471</v>
+        <v>25.51691874034421</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.260672044500372</v>
+        <v>1.401749189600638</v>
       </c>
       <c r="C21" t="n">
-        <v>11.18612169948154</v>
+        <v>11.07161064725819</v>
       </c>
       <c r="D21" t="n">
-        <v>5.787392899057906</v>
+        <v>6.731971635221932</v>
       </c>
       <c r="E21" t="n">
-        <v>18.23418664303982</v>
+        <v>19.20533147208076</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_83_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_83_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.265920894999173</v>
+        <v>2.591410944536368</v>
       </c>
       <c r="C3" t="n">
-        <v>4.584464200338379</v>
+        <v>7.771973417595252</v>
       </c>
       <c r="D3" t="n">
-        <v>6.101517897181875</v>
+        <v>8.190237845213479</v>
       </c>
       <c r="E3" t="n">
-        <v>11.95190299251943</v>
+        <v>18.5536222073451</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.409059329770022</v>
+        <v>1.066977098470282</v>
       </c>
       <c r="C4" t="n">
-        <v>5.018735742334273</v>
+        <v>4.646709011910962</v>
       </c>
       <c r="D4" t="n">
-        <v>6.323865010554353</v>
+        <v>5.780107934995112</v>
       </c>
       <c r="E4" t="n">
-        <v>12.75166008265865</v>
+        <v>11.49379404537636</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.602583396453214</v>
+        <v>1.150974650864398</v>
       </c>
       <c r="C5" t="n">
-        <v>5.571794519692975</v>
+        <v>5.498833572401591</v>
       </c>
       <c r="D5" t="n">
-        <v>6.673849699871101</v>
+        <v>6.176742852687617</v>
       </c>
       <c r="E5" t="n">
-        <v>13.84822761601729</v>
+        <v>12.82655107595361</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.841969546528976</v>
+        <v>1.237985862958257</v>
       </c>
       <c r="C6" t="n">
-        <v>6.252525442391349</v>
+        <v>6.5660157376445</v>
       </c>
       <c r="D6" t="n">
-        <v>7.088242410762389</v>
+        <v>6.549018376447521</v>
       </c>
       <c r="E6" t="n">
-        <v>15.18273739968271</v>
+        <v>14.35301997705028</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.119162018300665</v>
+        <v>1.324809593334966</v>
       </c>
       <c r="C7" t="n">
-        <v>7.055066526056532</v>
+        <v>7.870396275938008</v>
       </c>
       <c r="D7" t="n">
-        <v>7.488569792779955</v>
+        <v>7.003159797527323</v>
       </c>
       <c r="E7" t="n">
-        <v>16.66279833713715</v>
+        <v>16.1983656668003</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.376681997498973</v>
+        <v>1.410427493537014</v>
       </c>
       <c r="C8" t="n">
-        <v>4.778304451998786</v>
+        <v>9.315140002857284</v>
       </c>
       <c r="D8" t="n">
-        <v>5.784526270221582</v>
+        <v>7.460683599733877</v>
       </c>
       <c r="E8" t="n">
-        <v>11.93951271971934</v>
+        <v>18.18625109612817</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.769970822636691</v>
+        <v>1.476990179154278</v>
       </c>
       <c r="C9" t="n">
-        <v>5.903422036189775</v>
+        <v>10.98468266333223</v>
       </c>
       <c r="D9" t="n">
-        <v>6.36654579052012</v>
+        <v>7.994637562959676</v>
       </c>
       <c r="E9" t="n">
-        <v>14.03993864934659</v>
+        <v>20.45631040544618</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.176287177182393</v>
+        <v>0.9399252520458962</v>
       </c>
       <c r="C10" t="n">
-        <v>7.215529053485932</v>
+        <v>7.966362293679615</v>
       </c>
       <c r="D10" t="n">
-        <v>6.917480635209684</v>
+        <v>6.310468075880605</v>
       </c>
       <c r="E10" t="n">
-        <v>16.30929686587801</v>
+        <v>15.21675562160612</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.576405586999234</v>
+        <v>0.8412694252461342</v>
       </c>
       <c r="C11" t="n">
-        <v>8.698533504308587</v>
+        <v>8.782341898064352</v>
       </c>
       <c r="D11" t="n">
-        <v>7.565952397612882</v>
+        <v>6.216446098244889</v>
       </c>
       <c r="E11" t="n">
-        <v>18.8408914889207</v>
+        <v>15.84005742155538</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.971112409465879</v>
+        <v>0.8667850480795088</v>
       </c>
       <c r="C12" t="n">
-        <v>10.32418966640209</v>
+        <v>10.63972019720594</v>
       </c>
       <c r="D12" t="n">
-        <v>8.178216391046476</v>
+        <v>6.619885499828073</v>
       </c>
       <c r="E12" t="n">
-        <v>21.47351846691444</v>
+        <v>18.12639074511352</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.356878599672531</v>
+        <v>0.6617863099557324</v>
       </c>
       <c r="C13" t="n">
-        <v>12.03192569932913</v>
+        <v>10.30871414124208</v>
       </c>
       <c r="D13" t="n">
-        <v>8.808454313522692</v>
+        <v>6.064461736150441</v>
       </c>
       <c r="E13" t="n">
-        <v>24.19725861252435</v>
+        <v>17.03496218734826</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.921280257211008</v>
+        <v>0.6872037580186823</v>
       </c>
       <c r="C14" t="n">
-        <v>8.446515460872646</v>
+        <v>12.27605800073635</v>
       </c>
       <c r="D14" t="n">
-        <v>6.708419507797051</v>
+        <v>6.435788170327712</v>
       </c>
       <c r="E14" t="n">
-        <v>17.07621522588071</v>
+        <v>19.39904992908274</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.97598323929164</v>
+        <v>0.640825996470063</v>
       </c>
       <c r="C15" t="n">
-        <v>9.350518564420151</v>
+        <v>13.44045004788124</v>
       </c>
       <c r="D15" t="n">
-        <v>6.802510207772063</v>
+        <v>6.472034295568503</v>
       </c>
       <c r="E15" t="n">
-        <v>18.12901201148386</v>
+        <v>20.5533103399198</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.297093278396687</v>
+        <v>0.6790356171193488</v>
       </c>
       <c r="C16" t="n">
-        <v>11.17666746908964</v>
+        <v>15.7370524524258</v>
       </c>
       <c r="D16" t="n">
-        <v>7.357158390763344</v>
+        <v>6.91705071242654</v>
       </c>
       <c r="E16" t="n">
-        <v>20.83091913824967</v>
+        <v>23.33313878197169</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.84682451132093</v>
+        <v>0.4035473938306514</v>
       </c>
       <c r="C17" t="n">
-        <v>10.46604902832468</v>
+        <v>11.78543940301605</v>
       </c>
       <c r="D17" t="n">
-        <v>6.892644464498965</v>
+        <v>5.759442541917998</v>
       </c>
       <c r="E17" t="n">
-        <v>19.20551800414457</v>
+        <v>17.9484293387647</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.113555545087746</v>
+        <v>0.3001497256193774</v>
       </c>
       <c r="C18" t="n">
-        <v>12.27864981467556</v>
+        <v>10.86392192042478</v>
       </c>
       <c r="D18" t="n">
-        <v>7.392756562519331</v>
+        <v>5.25014128538588</v>
       </c>
       <c r="E18" t="n">
-        <v>21.78496192228264</v>
+        <v>16.41421293143004</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.122577806489774</v>
+        <v>0.340116674659265</v>
       </c>
       <c r="C19" t="n">
-        <v>13.17492656379064</v>
+        <v>13.44676268561954</v>
       </c>
       <c r="D19" t="n">
-        <v>7.528502817585538</v>
+        <v>5.710688950925102</v>
       </c>
       <c r="E19" t="n">
-        <v>22.82600718786595</v>
+        <v>19.49756831120391</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.359493162478615</v>
+        <v>0.3762842600837175</v>
       </c>
       <c r="C20" t="n">
-        <v>15.13132393638256</v>
+        <v>16.14517479055824</v>
       </c>
       <c r="D20" t="n">
-        <v>8.026101641483034</v>
+        <v>6.17444693145721</v>
       </c>
       <c r="E20" t="n">
-        <v>25.51691874034421</v>
+        <v>22.69590598209917</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.401749189600638</v>
+        <v>0.4038517356189679</v>
       </c>
       <c r="C21" t="n">
-        <v>11.07161064725819</v>
+        <v>18.72686691093903</v>
       </c>
       <c r="D21" t="n">
-        <v>6.731971635221932</v>
+        <v>6.545557381139547</v>
       </c>
       <c r="E21" t="n">
-        <v>19.20533147208076</v>
+        <v>25.67627602769755</v>
       </c>
     </row>
   </sheetData>
